--- a/data/trans_orig/P0901-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>41180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>39034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64949</t>
+          <t>64778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64731</t>
+          <t>67616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99731</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230564</t>
+          <t>231830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251889</t>
+          <t>252148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195889</t>
+          <t>196060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222013</t>
+          <t>221804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434117</t>
+          <t>432932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469117</t>
+          <t>466232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>62751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74501</t>
+          <t>74551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108478</t>
+          <t>109431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116216</t>
+          <t>116934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159587</t>
+          <t>159351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430244</t>
+          <t>430324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457936</t>
+          <t>457423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395471</t>
+          <t>394518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429448</t>
+          <t>429398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837437</t>
+          <t>837673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880808</t>
+          <t>880090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52269</t>
+          <t>51473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>83241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289047</t>
+          <t>288740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306355</t>
+          <t>306706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276186</t>
+          <t>275151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300312</t>
+          <t>300574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569859</t>
+          <t>571017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>601989</t>
+          <t>602785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46938</t>
+          <t>46757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74445</t>
+          <t>76275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>63652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96523</t>
+          <t>96248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329053</t>
+          <t>329998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347287</t>
+          <t>347275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297011</t>
+          <t>295181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324518</t>
+          <t>324699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633604</t>
+          <t>633879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666898</t>
+          <t>666475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>54332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179736</t>
+          <t>179252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194078</t>
+          <t>193777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171088</t>
+          <t>171738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191267</t>
+          <t>190914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>356644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381247</t>
+          <t>380474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>36116</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60541</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60194</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91146</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232897</t>
+          <t>233431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252538</t>
+          <t>252306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217603</t>
+          <t>217537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242406</t>
+          <t>242028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457809</t>
+          <t>458839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>488761</t>
+          <t>490030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75134</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71197</t>
+          <t>70926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107361</t>
+          <t>107853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127653</t>
+          <t>127261</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174455</t>
+          <t>170047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>539893</t>
+          <t>539741</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569406</t>
+          <t>569217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530858</t>
+          <t>530366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>567022</t>
+          <t>567293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1078791</t>
+          <t>1083199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1125593</t>
+          <t>1125985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>97461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>121285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162286</t>
+          <t>166895</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197588</t>
+          <t>191732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251135</t>
+          <t>249063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646701</t>
+          <t>646334</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>677887</t>
+          <t>678148</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>621225</t>
+          <t>616616</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>664994</t>
+          <t>662226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1276171</t>
+          <t>1278243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1329718</t>
+          <t>1335574</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>264385</t>
+          <t>264894</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>331126</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>507095</t>
+          <t>510656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>594358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>795998</t>
+          <t>795588</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>909314</t>
+          <t>900460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2945417</t>
+          <t>2940385</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3012158</t>
+          <t>3011649</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2782835</t>
+          <t>2784839</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2872102</t>
+          <t>2868541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5746427</t>
+          <t>5755281</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5859743</t>
+          <t>5860153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53848</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63480</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94806</t>
+          <t>95536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144183</t>
+          <t>140865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240890</t>
+          <t>240095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264340</t>
+          <t>264515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192439</t>
+          <t>191709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223765</t>
+          <t>223987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437800</t>
+          <t>441118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480320</t>
+          <t>480309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73166</t>
+          <t>73885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82579</t>
+          <t>82134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>118703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127878</t>
+          <t>131751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177885</t>
+          <t>181269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432361</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463660</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>404941</t>
+          <t>405062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441186</t>
+          <t>441631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>851407</t>
+          <t>848023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901414</t>
+          <t>897541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>54663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>84034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>89702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127309</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269624</t>
+          <t>269383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295130</t>
+          <t>295282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>256986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287922</t>
+          <t>287488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537757</t>
+          <t>536658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576974</t>
+          <t>575364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>45471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>75189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109970</t>
+          <t>109659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147028</t>
+          <t>147803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163036</t>
+          <t>164490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209588</t>
+          <t>211332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>295760</t>
+          <t>298793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>327554</t>
+          <t>328511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241923</t>
+          <t>241148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278981</t>
+          <t>279292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553345</t>
+          <t>551601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>599897</t>
+          <t>598443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>17819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67255</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99828</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175464</t>
+          <t>175563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194360</t>
+          <t>194799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150880</t>
+          <t>150521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177534</t>
+          <t>177162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332381</t>
+          <t>334675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364954</t>
+          <t>366446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>27372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>37682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>70298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104935</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225886</t>
+          <t>224524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247234</t>
+          <t>246609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217767</t>
+          <t>217635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244303</t>
+          <t>242349</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449077</t>
+          <t>450737</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485521</t>
+          <t>483714</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78887</t>
+          <t>79849</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90344</t>
+          <t>91198</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131405</t>
+          <t>130544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>147589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197808</t>
+          <t>197834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>583901</t>
+          <t>582939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614818</t>
+          <t>614281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>562448</t>
+          <t>563309</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603509</t>
+          <t>602655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1158833</t>
+          <t>1158807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1206989</t>
+          <t>1209052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>72673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112877</t>
+          <t>110893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133621</t>
+          <t>132266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178987</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217295</t>
+          <t>217344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278109</t>
+          <t>278528</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>666221</t>
+          <t>668205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>705787</t>
+          <t>706425</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>644866</t>
+          <t>645494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690232</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1324842</t>
+          <t>1324423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1385656</t>
+          <t>1385607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>377124</t>
+          <t>373017</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>452238</t>
+          <t>456133</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>692353</t>
+          <t>690758</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>785922</t>
+          <t>793204</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1091513</t>
+          <t>1089810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1219392</t>
+          <t>1217156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2974541</t>
+          <t>2970646</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3049655</t>
+          <t>3053762</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2772387</t>
+          <t>2765105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2865956</t>
+          <t>2867551</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5765696</t>
+          <t>5767932</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5893575</t>
+          <t>5895278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50977</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60066</t>
+          <t>62256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90766</t>
+          <t>93481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95014</t>
+          <t>93501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135471</t>
+          <t>133570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242784</t>
+          <t>244150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268100</t>
+          <t>267364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197937</t>
+          <t>195222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228637</t>
+          <t>226447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446993</t>
+          <t>448894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487450</t>
+          <t>488963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56254</t>
+          <t>55464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69726</t>
+          <t>69909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106946</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108424</t>
+          <t>107642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>153624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446321</t>
+          <t>447111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471038</t>
+          <t>471271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416138</t>
+          <t>417517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>453358</t>
+          <t>453175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870264</t>
+          <t>872035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917235</t>
+          <t>918017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>54811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54122</t>
+          <t>54478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85742</t>
+          <t>87173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281028</t>
+          <t>279676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299303</t>
+          <t>299118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>281912</t>
+          <t>281498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307639</t>
+          <t>306154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569132</t>
+          <t>567701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600752</t>
+          <t>600396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49382</t>
+          <t>49152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106048</t>
+          <t>108718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144564</t>
+          <t>147682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162917</t>
+          <t>162022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214257</t>
+          <t>213097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291230</t>
+          <t>291604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320582</t>
+          <t>320812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242719</t>
+          <t>239601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281235</t>
+          <t>278565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>542990</t>
+          <t>544150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594330</t>
+          <t>595225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>40455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184946</t>
+          <t>184523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200905</t>
+          <t>200615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179559</t>
+          <t>178132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198822</t>
+          <t>197643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368424</t>
+          <t>367697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394545</t>
+          <t>394159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33314</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>56574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80998</t>
+          <t>81320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93088</t>
+          <t>92332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131742</t>
+          <t>131461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205612</t>
+          <t>206549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229809</t>
+          <t>230652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192117</t>
+          <t>191795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222966</t>
+          <t>220676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>404496</t>
+          <t>404777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443150</t>
+          <t>443906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57783</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92639</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122419</t>
+          <t>124771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170039</t>
+          <t>169053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190168</t>
+          <t>189676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247796</t>
+          <t>246027</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563919</t>
+          <t>564254</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598775</t>
+          <t>598830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>521255</t>
+          <t>522241</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>568875</t>
+          <t>566523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1100056</t>
+          <t>1101825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157684</t>
+          <t>1158176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40865</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69291</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99092</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145473</t>
+          <t>142379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148194</t>
+          <t>147839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>200150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709292</t>
+          <t>709399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>738616</t>
+          <t>737718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>683788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>727075</t>
+          <t>726283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1402208</t>
+          <t>1404600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1456556</t>
+          <t>1456911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>322135</t>
+          <t>323257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>392663</t>
+          <t>393536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>641640</t>
+          <t>639480</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>740543</t>
+          <t>736634</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>981712</t>
+          <t>987151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107494</t>
+          <t>1107887</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3001687</t>
+          <t>3000814</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3072215</t>
+          <t>3071093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2803999</t>
+          <t>2807908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2902902</t>
+          <t>2905062</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5831398</t>
+          <t>5831005</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5957180</t>
+          <t>5951741</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46472</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52034</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>80540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270661</t>
+          <t>271469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291977</t>
+          <t>292149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243163</t>
+          <t>242215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260051</t>
+          <t>259922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521364</t>
+          <t>520537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549043</t>
+          <t>547865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73676</t>
+          <t>72458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111485</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109875</t>
+          <t>111696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142825</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194805</t>
+          <t>192179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244509</t>
+          <t>241598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406905</t>
+          <t>406723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>444714</t>
+          <t>445932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372144</t>
+          <t>371837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>405094</t>
+          <t>403273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>788850</t>
+          <t>791761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>838554</t>
+          <t>841180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>58723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54530</t>
+          <t>55052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78113</t>
+          <t>79434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97507</t>
+          <t>96965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130234</t>
+          <t>129115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257341</t>
+          <t>257327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280220</t>
+          <t>280039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270381</t>
+          <t>269060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293964</t>
+          <t>293442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534311</t>
+          <t>535430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567038</t>
+          <t>567580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>49071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78827</t>
+          <t>80071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58765</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124395</t>
+          <t>125729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114805</t>
+          <t>114923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192713</t>
+          <t>188602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233159</t>
+          <t>231915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>262915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351323</t>
+          <t>349989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>416953</t>
+          <t>418045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594991</t>
+          <t>599102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672899</t>
+          <t>672781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158019</t>
+          <t>159004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169676</t>
+          <t>169610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174701</t>
+          <t>174692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187337</t>
+          <t>186863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337417</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353481</t>
+          <t>353858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44634</t>
+          <t>43865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>65613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90624</t>
+          <t>90808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225002</t>
+          <t>225771</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244192</t>
+          <t>243306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204236</t>
+          <t>204018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221397</t>
+          <t>220936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436068</t>
+          <t>435884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>460866</t>
+          <t>461079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76258</t>
+          <t>75999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113686</t>
+          <t>114365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>70282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206894</t>
+          <t>209321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152587</t>
+          <t>160178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295935</t>
+          <t>293741</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>509503</t>
+          <t>508824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>546931</t>
+          <t>547190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642371</t>
+          <t>639944</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>769978</t>
+          <t>778983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1176518</t>
+          <t>1178712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1319866</t>
+          <t>1312275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116940</t>
+          <t>117687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132172</t>
+          <t>131167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>167804</t>
+          <t>167221</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136575</t>
+          <t>140516</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278835</t>
+          <t>282568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>811780</t>
+          <t>811033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894572</t>
+          <t>891259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>549927</t>
+          <t>550510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>585559</t>
+          <t>586564</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1367617</t>
+          <t>1363884</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1509877</t>
+          <t>1505936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>356462</t>
+          <t>344105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>503192</t>
+          <t>500524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>559095</t>
+          <t>566674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760672</t>
+          <t>762632</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1003297</t>
+          <t>990136</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1231605</t>
+          <t>1238738</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2954461</t>
+          <t>2957129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3101191</t>
+          <t>3113548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2899878</t>
+          <t>2897918</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3101455</t>
+          <t>3093876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5886597</t>
+          <t>5879464</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6114905</t>
+          <t>6128066</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0901-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41180</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>40712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64778</t>
+          <t>67039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67616</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100916</t>
+          <t>99116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231830</t>
+          <t>231613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252148</t>
+          <t>252387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196060</t>
+          <t>193799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221804</t>
+          <t>220126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432932</t>
+          <t>434732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466232</t>
+          <t>468436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>62028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>75700</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109431</t>
+          <t>108680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>116437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159351</t>
+          <t>159927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430324</t>
+          <t>431047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457423</t>
+          <t>457852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394518</t>
+          <t>395269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429398</t>
+          <t>428249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837673</t>
+          <t>837097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880090</t>
+          <t>880587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>34136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>52105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83241</t>
+          <t>82746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288740</t>
+          <t>288545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306706</t>
+          <t>306771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275151</t>
+          <t>275367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300574</t>
+          <t>301276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>571017</t>
+          <t>571512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>602785</t>
+          <t>602153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>29309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>76390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63652</t>
+          <t>64653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96248</t>
+          <t>96985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329998</t>
+          <t>329362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347275</t>
+          <t>347141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295181</t>
+          <t>295066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324699</t>
+          <t>323045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633879</t>
+          <t>633142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666475</t>
+          <t>665474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54332</t>
+          <t>53385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179252</t>
+          <t>179944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193777</t>
+          <t>194303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171738</t>
+          <t>171977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190914</t>
+          <t>191655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356644</t>
+          <t>357591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380474</t>
+          <t>381551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36116</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60607</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>60158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>92475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233431</t>
+          <t>232850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252306</t>
+          <t>252081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217537</t>
+          <t>217755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242028</t>
+          <t>241402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458839</t>
+          <t>456480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490030</t>
+          <t>488797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75286</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70926</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107853</t>
+          <t>106274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127261</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170047</t>
+          <t>170983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>539741</t>
+          <t>540273</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569217</t>
+          <t>569314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530366</t>
+          <t>531945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>567293</t>
+          <t>565300</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1083199</t>
+          <t>1082263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1125985</t>
+          <t>1128159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97461</t>
+          <t>97812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121285</t>
+          <t>119381</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>166895</t>
+          <t>165367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191732</t>
+          <t>194573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>249063</t>
+          <t>248814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646334</t>
+          <t>645983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>678148</t>
+          <t>678801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>616616</t>
+          <t>618144</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>662226</t>
+          <t>664130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1278243</t>
+          <t>1278492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1335574</t>
+          <t>1332733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>264894</t>
+          <t>266224</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>336158</t>
+          <t>332220</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>510656</t>
+          <t>509670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>594358</t>
+          <t>596973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>795588</t>
+          <t>795572</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>900460</t>
+          <t>901563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2940385</t>
+          <t>2944323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3011649</t>
+          <t>3010319</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2784839</t>
+          <t>2782224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2868541</t>
+          <t>2869527</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5755281</t>
+          <t>5754178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5860153</t>
+          <t>5860169</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63258</t>
+          <t>64346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95536</t>
+          <t>96208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140865</t>
+          <t>141334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240095</t>
+          <t>240211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264515</t>
+          <t>264663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191709</t>
+          <t>191037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223987</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>441118</t>
+          <t>440649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480309</t>
+          <t>482906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>40777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73885</t>
+          <t>72624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82134</t>
+          <t>80882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118703</t>
+          <t>120971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131751</t>
+          <t>131720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181269</t>
+          <t>179133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431642</t>
+          <t>432903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463172</t>
+          <t>464750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405062</t>
+          <t>402794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441631</t>
+          <t>442883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848023</t>
+          <t>850159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>897541</t>
+          <t>897572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84034</t>
+          <t>82418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>87850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128408</t>
+          <t>128017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269383</t>
+          <t>270094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295282</t>
+          <t>294701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256986</t>
+          <t>258602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287488</t>
+          <t>287655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>536658</t>
+          <t>537049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575364</t>
+          <t>577216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75189</t>
+          <t>76568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>108763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147803</t>
+          <t>147010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164490</t>
+          <t>163138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211332</t>
+          <t>209964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298793</t>
+          <t>297414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328511</t>
+          <t>326673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241148</t>
+          <t>241941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279292</t>
+          <t>280188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>551601</t>
+          <t>552969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>598443</t>
+          <t>599795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69070</t>
+          <t>68069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65763</t>
+          <t>66533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97534</t>
+          <t>99222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175563</t>
+          <t>175153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194799</t>
+          <t>194294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150521</t>
+          <t>151522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177162</t>
+          <t>176167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334675</t>
+          <t>332987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366446</t>
+          <t>365676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37682</t>
+          <t>36403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62396</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70298</t>
+          <t>69257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103275</t>
+          <t>104585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224524</t>
+          <t>224822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246609</t>
+          <t>246823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217635</t>
+          <t>219624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242349</t>
+          <t>243628</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450737</t>
+          <t>449427</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>483714</t>
+          <t>484755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>46865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79849</t>
+          <t>78568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91198</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130544</t>
+          <t>131392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>147589</t>
+          <t>147677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>199116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>582939</t>
+          <t>584220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614281</t>
+          <t>615923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>563309</t>
+          <t>562461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602655</t>
+          <t>603238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1158807</t>
+          <t>1157525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209052</t>
+          <t>1208964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>69393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110893</t>
+          <t>110333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132266</t>
+          <t>132431</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178359</t>
+          <t>178960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217344</t>
+          <t>214695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278528</t>
+          <t>273453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>668205</t>
+          <t>668765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>706425</t>
+          <t>709705</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645494</t>
+          <t>644893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>691422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1324423</t>
+          <t>1329498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1385607</t>
+          <t>1388256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>373017</t>
+          <t>372736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>456133</t>
+          <t>457774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>690758</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>793204</t>
+          <t>793882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1089810</t>
+          <t>1091529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1217156</t>
+          <t>1218293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2970646</t>
+          <t>2969005</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3053762</t>
+          <t>3054043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2765105</t>
+          <t>2764427</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2867551</t>
+          <t>2864106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5767932</t>
+          <t>5766795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5895278</t>
+          <t>5893559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62256</t>
+          <t>60838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93481</t>
+          <t>91667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93501</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133570</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>243373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267364</t>
+          <t>268094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195222</t>
+          <t>197036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226447</t>
+          <t>227865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448894</t>
+          <t>451104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488963</t>
+          <t>490378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55464</t>
+          <t>56885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69909</t>
+          <t>69231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105567</t>
+          <t>105344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107642</t>
+          <t>109336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153624</t>
+          <t>152860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447111</t>
+          <t>445690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471271</t>
+          <t>471366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417517</t>
+          <t>417740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>453175</t>
+          <t>453853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872035</t>
+          <t>872799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918017</t>
+          <t>916323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87173</t>
+          <t>87166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279676</t>
+          <t>279809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299118</t>
+          <t>299290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>281498</t>
+          <t>280254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306154</t>
+          <t>306041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567701</t>
+          <t>567708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600396</t>
+          <t>601251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>79012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108718</t>
+          <t>106783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>146521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162022</t>
+          <t>163568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213097</t>
+          <t>214237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291604</t>
+          <t>290952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320812</t>
+          <t>321030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239601</t>
+          <t>240762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278565</t>
+          <t>280500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>544150</t>
+          <t>543010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595225</t>
+          <t>593679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62111</t>
+          <t>59008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184523</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200615</t>
+          <t>201216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178132</t>
+          <t>179401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197643</t>
+          <t>199193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367697</t>
+          <t>370800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394159</t>
+          <t>394707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56574</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52439</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81320</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92332</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131461</t>
+          <t>132058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206549</t>
+          <t>205446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230652</t>
+          <t>229837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191795</t>
+          <t>190714</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220676</t>
+          <t>219542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>404777</t>
+          <t>404180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443906</t>
+          <t>444596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>56611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92304</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124771</t>
+          <t>123178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169053</t>
+          <t>167999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,47 +9487,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>216437</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>188618</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>243343</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>18,05%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>216437</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>189676</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>246027</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564254</t>
+          <t>565649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598830</t>
+          <t>599947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>522241</t>
+          <t>523295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>566523</t>
+          <t>568116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,47 +9600,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1131415</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1104509</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1159234</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>81,95%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1131415</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1101825</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1158176</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>81,75%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69184</t>
+          <t>69002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99884</t>
+          <t>95764</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142379</t>
+          <t>141166</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147839</t>
+          <t>147725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>200150</t>
+          <t>198778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709399</t>
+          <t>709581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>737718</t>
+          <t>737744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>683788</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>726283</t>
+          <t>730403</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1404600</t>
+          <t>1405972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1456911</t>
+          <t>1457025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>323257</t>
+          <t>319716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>393536</t>
+          <t>394196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>639480</t>
+          <t>635291</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>736634</t>
+          <t>741820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>987151</t>
+          <t>976514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107887</t>
+          <t>1106741</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3000814</t>
+          <t>3000154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3071093</t>
+          <t>3074634</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2807908</t>
+          <t>2802722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2905062</t>
+          <t>2909251</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5831005</t>
+          <t>5832151</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5951741</t>
+          <t>5962378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53212</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80540</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>283175</t>
+          <t>290974</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271469</t>
+          <t>279955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292149</t>
+          <t>298600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252579</t>
+          <t>273612</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242215</t>
+          <t>262934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259922</t>
+          <t>282423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>535753</t>
+          <t>564586</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520537</t>
+          <t>549866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>547865</t>
+          <t>576971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91091</t>
+          <t>96214</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72458</t>
+          <t>78413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111667</t>
+          <t>117995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126671</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111696</t>
+          <t>115056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>149878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>217763</t>
+          <t>227824</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192179</t>
+          <t>202368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241598</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>427299</t>
+          <t>434433</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406723</t>
+          <t>412652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445932</t>
+          <t>452234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>388298</t>
+          <t>414884</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371837</t>
+          <t>396616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403273</t>
+          <t>431438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>815596</t>
+          <t>849317</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791761</t>
+          <t>820136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>841180</t>
+          <t>874773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>35195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>56758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66140</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55052</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>77663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>112153</t>
+          <t>110622</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96965</t>
+          <t>96198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129115</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>270037</t>
+          <t>271279</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257327</t>
+          <t>259235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280039</t>
+          <t>280798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>282354</t>
+          <t>289829</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269060</t>
+          <t>278074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293442</t>
+          <t>300486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>552392</t>
+          <t>561109</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535430</t>
+          <t>545626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567580</t>
+          <t>575533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>355737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>70159</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>54320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96650</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>89766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125729</t>
+          <t>122549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>159241</t>
+          <t>176193</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114923</t>
+          <t>152947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188602</t>
+          <t>202696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>249395</t>
+          <t>302400</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231915</t>
+          <t>281675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262915</t>
+          <t>318239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>379068</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349989</t>
+          <t>299412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>418045</t>
+          <t>332195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>628463</t>
+          <t>618327</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>599102</t>
+          <t>591824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672781</t>
+          <t>641573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787704</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>22140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165272</t>
+          <t>191241</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159004</t>
+          <t>184847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169610</t>
+          <t>196090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>181075</t>
+          <t>197966</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174692</t>
+          <t>190898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186863</t>
+          <t>204030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>346346</t>
+          <t>389207</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337426</t>
+          <t>380265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353858</t>
+          <t>396739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385921</t>
+          <t>431342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>42679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>64789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90808</t>
+          <t>90589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235976</t>
+          <t>237890</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225771</t>
+          <t>228028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243306</t>
+          <t>246265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>213535</t>
+          <t>219469</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204018</t>
+          <t>209902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220936</t>
+          <t>227433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>449510</t>
+          <t>457359</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435884</t>
+          <t>443868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461079</t>
+          <t>469668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>92879</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75999</t>
+          <t>84974</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114365</t>
+          <t>126557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>153030</t>
+          <t>190045</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>170835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209321</t>
+          <t>211523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>245909</t>
+          <t>293931</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160178</t>
+          <t>266377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293741</t>
+          <t>325725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>530310</t>
+          <t>614697</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>508824</t>
+          <t>592026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>547190</t>
+          <t>633609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>696235</t>
+          <t>582012</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>639944</t>
+          <t>560534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>778983</t>
+          <t>601222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1226544</t>
+          <t>1196709</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1178712</t>
+          <t>1164915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312275</t>
+          <t>1224263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623189</t>
+          <t>718583</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623189</t>
+          <t>718583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623189</t>
+          <t>718583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472453</t>
+          <t>1490640</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472453</t>
+          <t>1490640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472453</t>
+          <t>1490640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>75711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>148357</t>
+          <t>165501</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131167</t>
+          <t>147133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>167221</t>
+          <t>185789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>229606</t>
+          <t>256912</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>140516</t>
+          <t>233070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282568</t>
+          <t>283928</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>847471</t>
+          <t>706662</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>811033</t>
+          <t>686255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>891259</t>
+          <t>722361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>569374</t>
+          <t>665830</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>550510</t>
+          <t>645542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>586564</t>
+          <t>684198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1416846</t>
+          <t>1372491</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1363884</t>
+          <t>1345475</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1505936</t>
+          <t>1396333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>438177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>500524</t>
+          <t>522614</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>566674</t>
+          <t>734684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>762632</t>
+          <t>817138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>990136</t>
+          <t>1194796</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1238738</t>
+          <t>1324056</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3008934</t>
+          <t>3049576</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2957129</t>
+          <t>3007965</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3113548</t>
+          <t>3092402</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2962517</t>
+          <t>2959531</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2897918</t>
+          <t>2916425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3093876</t>
+          <t>2998879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5971450</t>
+          <t>6009107</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5879464</t>
+          <t>5940086</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6128066</t>
+          <t>6069346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
